--- a/artfynd/A 13006-2022 artfynd.xlsx
+++ b/artfynd/A 13006-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13006-2022 artfynd.xlsx
+++ b/artfynd/A 13006-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3050291</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113367370</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113367371</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113367373</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113367392</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113367393</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,8 +1431,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113367400</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 13006-2022 artfynd.xlsx
+++ b/artfynd/A 13006-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>3050291</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>99242</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13006-2022 artfynd.xlsx
+++ b/artfynd/A 13006-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>3050291</v>
       </c>
       <c r="B2" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13006-2022 artfynd.xlsx
+++ b/artfynd/A 13006-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113367370</v>
+        <v>3050291</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>99274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,27 +710,32 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Madhagen, Sm</t>
+          <t>vetlanda 1 km väster om karlslund, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502917</v>
+        <v>503200</v>
       </c>
       <c r="R2" t="n">
-        <v>6365600</v>
+        <v>6365835</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +759,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2011-08-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2011-08-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>utbrett ca 50m radie</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,28 +780,33 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gran-Tallskog</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jakob Wilhelmsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
+          <t>Jakob Wilhelmsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113367370</t>
+          <t>https://artportalen.se/Sighting/3050291</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113367371</v>
+        <v>113367370</v>
       </c>
       <c r="B3" t="n">
         <v>99118</v>
@@ -821,7 +836,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -830,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502885</v>
+        <v>502917</v>
       </c>
       <c r="R3" t="n">
-        <v>6365532</v>
+        <v>6365600</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +880,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,13 +911,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113367371</t>
+          <t>https://artportalen.se/Sighting/113367370</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113367373</v>
+        <v>113367371</v>
       </c>
       <c r="B4" t="n">
         <v>99118</v>
@@ -925,17 +945,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Madhagen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502821</v>
+        <v>502885</v>
       </c>
       <c r="R4" t="n">
-        <v>6365428</v>
+        <v>6365532</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,13 +1017,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113367373</t>
+          <t>https://artportalen.se/Sighting/113367371</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113367392</v>
+        <v>113367373</v>
       </c>
       <c r="B5" t="n">
         <v>99118</v>
@@ -1027,21 +1051,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Madhagen, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503448</v>
+        <v>502821</v>
       </c>
       <c r="R5" t="n">
-        <v>6365997</v>
+        <v>6365428</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1068,12 +1088,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2022-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,13 +1119,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113367392</t>
+          <t>https://artportalen.se/Sighting/113367373</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113367393</v>
+        <v>113367392</v>
       </c>
       <c r="B6" t="n">
         <v>99118</v>
@@ -1135,7 +1155,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1144,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503454</v>
+        <v>503448</v>
       </c>
       <c r="R6" t="n">
-        <v>6365982</v>
+        <v>6365997</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,12 +1194,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-11-15</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,51 +1225,55 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113367393</t>
+          <t>https://artportalen.se/Sighting/113367392</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113367400</v>
+        <v>113367393</v>
       </c>
       <c r="B7" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Madhagen, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502823</v>
+        <v>503454</v>
       </c>
       <c r="R7" t="n">
-        <v>6365452</v>
+        <v>6365982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,12 +1300,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,6 +1330,108 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113367393</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>113367400</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Madhagen, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>502823</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6365452</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tomas Fasth</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/113367400</t>
         </is>
@@ -1319,6 +1445,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13006-2022 artfynd.xlsx
+++ b/artfynd/A 13006-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>3050291</v>
       </c>
       <c r="B2" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13006-2022 artfynd.xlsx
+++ b/artfynd/A 13006-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>3050291</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13006-2022 artfynd.xlsx
+++ b/artfynd/A 13006-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>3050291</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13006-2022 artfynd.xlsx
+++ b/artfynd/A 13006-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>3050291</v>
       </c>
       <c r="B2" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 13006-2022 artfynd.xlsx
+++ b/artfynd/A 13006-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>3050291</v>
       </c>
       <c r="B2" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
